--- a/artfynd/A 32321-2026 artfynd.xlsx
+++ b/artfynd/A 32321-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137259776</v>
       </c>
       <c r="B2" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32321-2026 artfynd.xlsx
+++ b/artfynd/A 32321-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137259776</v>
       </c>
       <c r="B2" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -774,12 +774,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Viktor Leo</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktor Lund, Viktor Åberg, Jesper Hansson</t>
+          <t>Viktor Leo, Viktor Åberg, Jesper Hansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 32321-2026 artfynd.xlsx
+++ b/artfynd/A 32321-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137259776</v>
       </c>
       <c r="B2" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32321-2026 artfynd.xlsx
+++ b/artfynd/A 32321-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137259776</v>
       </c>
       <c r="B2" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32321-2026 artfynd.xlsx
+++ b/artfynd/A 32321-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137259776</v>
       </c>
       <c r="B2" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32321-2026 artfynd.xlsx
+++ b/artfynd/A 32321-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137259776</v>
       </c>
       <c r="B2" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32321-2026 artfynd.xlsx
+++ b/artfynd/A 32321-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137259776</v>
       </c>
       <c r="B2" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32321-2026 artfynd.xlsx
+++ b/artfynd/A 32321-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137259776</v>
       </c>
       <c r="B2" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32321-2026 artfynd.xlsx
+++ b/artfynd/A 32321-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137259776</v>
       </c>
       <c r="B2" t="n">
-        <v>91659</v>
+        <v>91663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
